--- a/Outputs/Scenarios/PtX_demand_RO_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_RO_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002484745587897071</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002823900300177805</v>
+        <v>0.003651739830231575</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.004706500500296342</v>
+        <v>0.004032882819252777</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>3.580097795272014e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001882600200118537</v>
+        <v>0.001728378351108333</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.003678363334053432</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01504512296751427</v>
+        <v>0.0194556708633603</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02507520494585712</v>
+        <v>0.02148631731984775</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0001935980702133385</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01003008197834285</v>
+        <v>0.00920842170850618</v>
       </c>
     </row>
     <row r="43">
